--- a/santhosh/Daily Activity/Santhosh DA Log.xlsx
+++ b/santhosh/Daily Activity/Santhosh DA Log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="201">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -367,6 +367,12 @@
   </si>
   <si>
     <t xml:space="preserve">checked jobs in centra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reports assigned by TL (Inprogess), wf14(inprogress)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wf13 is inprogress because of a bug</t>
   </si>
   <si>
     <t xml:space="preserve">Server</t>
@@ -1471,9 +1477,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultColWidth="19.36328125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="19.3828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="41.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="39.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="20.23"/>
   </cols>
@@ -2063,6 +2069,12 @@
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
         <v>45622</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2082,7 +2094,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="25.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="9" width="59.06"/>
@@ -2093,13 +2105,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2107,13 +2119,13 @@
         <v>45590</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2121,13 +2133,13 @@
         <v>45590</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2135,13 +2147,13 @@
         <v>45590</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="D4" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2149,13 +2161,13 @@
         <v>45590</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2163,13 +2175,13 @@
         <v>45591</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2177,13 +2189,13 @@
         <v>45591</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2191,13 +2203,13 @@
         <v>45591</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2205,13 +2217,13 @@
         <v>45591</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2219,13 +2231,13 @@
         <v>45591</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2233,13 +2245,13 @@
         <v>45591</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2251,13 +2263,13 @@
         <v>45594</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2265,13 +2277,13 @@
         <v>45594</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2279,13 +2291,13 @@
         <v>45595</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2293,13 +2305,13 @@
         <v>45595</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2307,13 +2319,13 @@
         <v>45595</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>62</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2352,49 +2364,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L1" s="18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M1" s="18" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N1" s="18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O1" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P1" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="250.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2405,28 +2417,28 @@
         <v>79</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F2" s="23" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K2" s="23"/>
       <c r="L2" s="23"/>
@@ -2440,29 +2452,29 @@
         <v>45601</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="26" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F3" s="26" t="s">
         <v>35</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J3" s="23" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K3" s="27"/>
       <c r="L3" s="28"/>
@@ -2476,26 +2488,26 @@
         <v>45601</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D4" s="25"/>
       <c r="E4" s="26" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F4" s="26" t="s">
         <v>35</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J4" s="23"/>
       <c r="K4" s="0"/>
@@ -2510,32 +2522,32 @@
         <v>45602</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D5" s="31"/>
       <c r="E5" s="31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>48</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="58.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2543,28 +2555,28 @@
         <v>45602</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="172.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2572,32 +2584,32 @@
         <v>45603</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="23" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2605,26 +2617,26 @@
         <v>45603</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="47.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2632,16 +2644,16 @@
         <v>45604</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>48</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2649,13 +2661,13 @@
         <v>45604</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="136.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2663,10 +2675,10 @@
         <v>45604</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>27</v>
@@ -2680,7 +2692,7 @@
         <v>78</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
